--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26205" windowHeight="7740"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>对账单号</t>
   </si>
@@ -37,6 +37,12 @@
     <t>单据状态</t>
   </si>
   <si>
+    <t>付款状态</t>
+  </si>
+  <si>
+    <t>付款时间</t>
+  </si>
+  <si>
     <t>对账周期</t>
   </si>
   <si>
@@ -77,6 +83,12 @@
   </si>
   <si>
     <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.payStatusName}</t>
+  </si>
+  <si>
+    <t>{.payTime}</t>
   </si>
   <si>
     <t>{.cycle}</t>
@@ -1043,26 +1055,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="14.75" customWidth="1"/>
-    <col min="4" max="4" width="21.625" customWidth="1"/>
-    <col min="5" max="5" width="18.875" customWidth="1"/>
-    <col min="6" max="6" width="24.125" customWidth="1"/>
-    <col min="7" max="7" width="21.75" customWidth="1"/>
-    <col min="8" max="8" width="20.375" customWidth="1"/>
-    <col min="9" max="9" width="19.375" customWidth="1"/>
-    <col min="10" max="10" width="15.125" customWidth="1"/>
-    <col min="11" max="11" width="23.75" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="17.375" customWidth="1"/>
-    <col min="14" max="14" width="15.625" customWidth="1"/>
+    <col min="3" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="21.625" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="24.125" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
+    <col min="10" max="10" width="20.375" customWidth="1"/>
+    <col min="11" max="11" width="19.375" customWidth="1"/>
+    <col min="12" max="12" width="15.125" customWidth="1"/>
+    <col min="13" max="13" width="23.75" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="17.375" customWidth="1"/>
+    <col min="16" max="16" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1105,49 +1117,61 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N2" t="s">
-        <v>27</v>
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>对账单号</t>
   </si>
@@ -64,9 +64,6 @@
     <t>实际计费重量</t>
   </si>
   <si>
-    <t>结算币种</t>
-  </si>
-  <si>
     <t>生成对账日期</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
   </si>
   <si>
     <t>{.actualBillingWeight}</t>
-  </si>
-  <si>
-    <t>{.currency}</t>
   </si>
   <si>
     <t>{.reconciliationDate}</t>
@@ -1055,7 +1049,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -1067,14 +1061,13 @@
     <col min="9" max="9" width="21.75" customWidth="1"/>
     <col min="10" max="10" width="20.375" customWidth="1"/>
     <col min="11" max="11" width="19.375" customWidth="1"/>
-    <col min="12" max="12" width="15.125" customWidth="1"/>
-    <col min="13" max="13" width="23.75" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="17.375" customWidth="1"/>
-    <col min="16" max="16" width="15.625" customWidth="1"/>
+    <col min="12" max="12" width="23.75" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="17.375" customWidth="1"/>
+    <col min="15" max="15" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1120,58 +1113,52 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>29</v>
-      </c>
-      <c r="O2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>对账单号</t>
   </si>
@@ -58,6 +58,9 @@
     <t>实际报关费用</t>
   </si>
   <si>
+    <t>实际其他税费</t>
+  </si>
+  <si>
     <t>实际其他费用</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
   </si>
   <si>
     <t>{.actualDeclareCost}</t>
+  </si>
+  <si>
+    <t>{.actualOtherTaxCost}</t>
   </si>
   <si>
     <t>{.actualOtherCost}</t>
@@ -1049,7 +1055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
@@ -1058,16 +1064,16 @@
     <col min="6" max="6" width="21.625" customWidth="1"/>
     <col min="7" max="7" width="18.875" customWidth="1"/>
     <col min="8" max="8" width="24.125" customWidth="1"/>
-    <col min="9" max="9" width="21.75" customWidth="1"/>
-    <col min="10" max="10" width="20.375" customWidth="1"/>
-    <col min="11" max="11" width="19.375" customWidth="1"/>
-    <col min="12" max="12" width="23.75" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="17.375" customWidth="1"/>
-    <col min="15" max="15" width="15.625" customWidth="1"/>
+    <col min="9" max="10" width="21.75" customWidth="1"/>
+    <col min="11" max="11" width="20.375" customWidth="1"/>
+    <col min="12" max="12" width="19.375" customWidth="1"/>
+    <col min="13" max="13" width="23.75" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="17.375" customWidth="1"/>
+    <col min="16" max="16" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1113,52 +1119,58 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
     <t>实际物流运费</t>
   </si>
   <si>
-    <t>实际报关费用</t>
+    <t>实际关税费用</t>
   </si>
   <si>
     <t>实际其他税费</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliation.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>对账单号</t>
   </si>
@@ -46,6 +46,9 @@
     <t>对账周期</t>
   </si>
   <si>
+    <t>对账类型</t>
+  </si>
+  <si>
     <t>物流商</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
   </si>
   <si>
     <t>{.cycle}</t>
+  </si>
+  <si>
+    <t>{.supplierTypeName}</t>
   </si>
   <si>
     <t>{.logisticsSupplierName}</t>
@@ -1055,25 +1061,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="14.375" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="5" width="14.75" customWidth="1"/>
-    <col min="6" max="6" width="21.625" customWidth="1"/>
-    <col min="7" max="7" width="18.875" customWidth="1"/>
-    <col min="8" max="8" width="24.125" customWidth="1"/>
-    <col min="9" max="10" width="21.75" customWidth="1"/>
-    <col min="11" max="11" width="20.375" customWidth="1"/>
-    <col min="12" max="12" width="19.375" customWidth="1"/>
-    <col min="13" max="13" width="23.75" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="17.375" customWidth="1"/>
-    <col min="16" max="16" width="15.625" customWidth="1"/>
+    <col min="6" max="7" width="21.625" customWidth="1"/>
+    <col min="8" max="8" width="18.875" customWidth="1"/>
+    <col min="9" max="9" width="24.125" customWidth="1"/>
+    <col min="10" max="11" width="21.75" customWidth="1"/>
+    <col min="12" max="12" width="20.375" customWidth="1"/>
+    <col min="13" max="13" width="19.375" customWidth="1"/>
+    <col min="14" max="14" width="23.75" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="17.375" customWidth="1"/>
+    <col min="17" max="17" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1122,55 +1128,61 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
